--- a/artfynd/A 37406-2022 artfynd.xlsx
+++ b/artfynd/A 37406-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37406-2022 artfynd.xlsx
+++ b/artfynd/A 37406-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91841269</v>
+        <v>91953984</v>
       </c>
       <c r="B2" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436349.8804941672</v>
+        <v>436231</v>
       </c>
       <c r="R2" t="n">
-        <v>6970040.799606742</v>
+        <v>6969914</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +743,9 @@
           <t>2019-06-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-10-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91841267</v>
+        <v>91841291</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436349.8804941672</v>
+        <v>436326</v>
       </c>
       <c r="R3" t="n">
-        <v>6970040.799606742</v>
+        <v>6970026</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +844,9 @@
           <t>2019-06-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-10-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>91841266</v>
+        <v>91841267</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436349.8804941672</v>
+        <v>436350</v>
       </c>
       <c r="R4" t="n">
-        <v>6970040.799606742</v>
+        <v>6970041</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +945,9 @@
           <t>2019-06-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-10-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,16 +981,11 @@
         <v>91841270</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436349.8804941672</v>
+        <v>436350</v>
       </c>
       <c r="R5" t="n">
-        <v>6970040.799606742</v>
+        <v>6970041</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,19 +1046,9 @@
           <t>2019-06-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-10-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>91841291</v>
+        <v>91953992</v>
       </c>
       <c r="B6" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,13 +1114,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436325.8126503874</v>
+        <v>436351</v>
       </c>
       <c r="R6" t="n">
-        <v>6970026.19456895</v>
+        <v>6970051</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,19 +1147,9 @@
           <t>2019-06-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2019-10-31</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>91953991</v>
+        <v>91841269</v>
       </c>
       <c r="B7" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,13 +1215,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436350.9900215057</v>
+        <v>436350</v>
       </c>
       <c r="R7" t="n">
-        <v>6970050.826425609</v>
+        <v>6970041</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,19 +1248,9 @@
           <t>2019-06-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2019-10-31</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>91954000</v>
+        <v>91953990</v>
       </c>
       <c r="B8" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436350.0223880522</v>
+        <v>436351</v>
       </c>
       <c r="R8" t="n">
-        <v>6970048.104759119</v>
+        <v>6970051</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1444,19 +1349,14 @@
           <t>2019-06-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2019-10-31</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,15 +1387,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>91953992</v>
+        <v>91953995</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,21 +1398,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1527,10 +1422,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436350.9900215057</v>
+        <v>435958</v>
       </c>
       <c r="R9" t="n">
-        <v>6970050.826425609</v>
+        <v>6970135</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1560,19 +1455,14 @@
           <t>2019-06-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2019-10-31</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,15 +1493,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>91953995</v>
+        <v>91953999</v>
       </c>
       <c r="B10" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,10 +1528,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435957.9157911548</v>
+        <v>436350</v>
       </c>
       <c r="R10" t="n">
-        <v>6970135.217124478</v>
+        <v>6970048</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1676,24 +1561,9 @@
           <t>2019-06-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2019-10-31</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1724,15 +1594,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>91953984</v>
+        <v>106029927</v>
       </c>
       <c r="B11" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,37 +1605,45 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Stavbrännhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436230.7768107675</v>
+        <v>436045</v>
       </c>
       <c r="R11" t="n">
-        <v>6969913.853788217</v>
+        <v>6970047</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1794,22 +1667,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-16</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,31 +1692,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>91953999</v>
+        <v>106029928</v>
       </c>
       <c r="B12" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1874,19 +1733,27 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Stavbrännhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436350.0223880522</v>
+        <v>436106</v>
       </c>
       <c r="R12" t="n">
-        <v>6970048.104759119</v>
+        <v>6969972</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1910,22 +1777,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,31 +1802,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>91953990</v>
+        <v>106029929</v>
       </c>
       <c r="B13" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1990,19 +1843,27 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Stavbrännhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436350.9900215057</v>
+        <v>436217</v>
       </c>
       <c r="R13" t="n">
-        <v>6970050.826425609</v>
+        <v>6969893</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2026,27 +1887,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-16</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,31 +1912,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>106029929</v>
+        <v>106029930</v>
       </c>
       <c r="B14" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2115,7 +1957,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2125,10 +1967,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436216.6510923142</v>
+        <v>436191</v>
       </c>
       <c r="R14" t="n">
-        <v>6969893.117519733</v>
+        <v>6970145</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2158,19 +2000,9 @@
           <t>2023-01-16</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-01-16</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2205,12 +2037,7 @@
         <v>106029931</v>
       </c>
       <c r="B15" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2250,10 +2077,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436117.2553247804</v>
+        <v>436117</v>
       </c>
       <c r="R15" t="n">
-        <v>6970191.024947384</v>
+        <v>6970191</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2283,19 +2110,9 @@
           <t>2023-01-16</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-01-16</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2327,15 +2144,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>106029927</v>
+        <v>106029932</v>
       </c>
       <c r="B16" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2365,7 +2177,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2375,10 +2187,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436044.9285013824</v>
+        <v>436077</v>
       </c>
       <c r="R16" t="n">
-        <v>6970047.193875467</v>
+        <v>6970186</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2408,19 +2220,9 @@
           <t>2023-01-16</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-01-16</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2452,15 +2254,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>106029930</v>
+        <v>106029940</v>
       </c>
       <c r="B17" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2490,7 +2287,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2500,10 +2297,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436190.9064006988</v>
+        <v>436350</v>
       </c>
       <c r="R17" t="n">
-        <v>6970144.830515782</v>
+        <v>6969908</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2533,24 +2330,14 @@
           <t>2023-01-16</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-01-16</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>brutet träd med bohål</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2574,381 +2361,6 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>106029928</v>
-      </c>
-      <c r="B18" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Stavbrännhöjden, Jmt</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>436106.1244471658</v>
-      </c>
-      <c r="R18" t="n">
-        <v>6969972.006478533</v>
-      </c>
-      <c r="S18" t="n">
-        <v>10</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Oviken</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2023-01-16</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2023-01-16</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>106029940</v>
-      </c>
-      <c r="B19" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Stavbrännhöjden, Jmt</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>436349.5859166033</v>
-      </c>
-      <c r="R19" t="n">
-        <v>6969907.889909287</v>
-      </c>
-      <c r="S19" t="n">
-        <v>10</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Oviken</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2023-01-16</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2023-01-16</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>brutet träd med bohål</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>106029932</v>
-      </c>
-      <c r="B20" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Stavbrännhöjden, Jmt</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>436077.3549114628</v>
-      </c>
-      <c r="R20" t="n">
-        <v>6970185.408922471</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Oviken</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2023-01-16</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2023-01-16</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37406-2022 artfynd.xlsx
+++ b/artfynd/A 37406-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91953984</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91953995</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106029927</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106029928</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1209,6 +1234,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106029929</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,6 +1349,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106029930</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1429,6 +1464,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106029931</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1539,6 +1579,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106029932</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1640,6 +1685,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91841291</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1741,6 +1791,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91841267</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1842,6 +1897,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91841270</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1943,6 +2003,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91953992</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2044,6 +2109,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91841269</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2150,6 +2220,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91953990</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2251,6 +2326,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91953999</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2361,8 +2441,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106029940</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>